--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3018867924528302</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="C2">
-        <v>0.2887323943661972</v>
+        <v>0.2746478873239437</v>
       </c>
       <c r="D2">
-        <v>0.8632478632478633</v>
+        <v>0.8046875</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
